--- a/sample_data/erzeugt/Quotation_Nordtec_mit_Stoerfaellen.xlsx
+++ b/sample_data/erzeugt/Quotation_Nordtec_mit_Stoerfaellen.xlsx
@@ -437,7 +437,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Date: 2026-08-17</t>
+          <t>Date: 2026-08-18</t>
         </is>
       </c>
     </row>
